--- a/data/trans_orig/IQ2606_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2012 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40133</t>
+          <t>39605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59679</t>
+          <t>59553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49152</t>
+          <t>48699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70004</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95068</t>
+          <t>95560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>123777</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37355</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44588</t>
+          <t>46385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>68517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22270</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>39035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36208</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>58174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18062</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29329</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42135</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64599</t>
+          <t>64273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70830</t>
+          <t>70006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91952</t>
+          <t>93053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62526</t>
+          <t>62892</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>85599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138676</t>
+          <t>139574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170866</t>
+          <t>170860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56212</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>36164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56230</t>
+          <t>56002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78188</t>
+          <t>78018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103944</t>
+          <t>104097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28812</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47159</t>
+          <t>47157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>28718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>46887</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>62999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87826</t>
+          <t>87123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>14859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>31495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>64332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82693</t>
+          <t>83455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65509</t>
+          <t>66133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85461</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>135687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164508</t>
+          <t>164083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>40038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59682</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56590</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20681</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29223</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36465</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>40136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>61104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66049</t>
+          <t>66186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89456</t>
+          <t>89676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58570</t>
+          <t>57352</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81266</t>
+          <t>80305</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>131520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164700</t>
+          <t>164106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38217</t>
+          <t>38448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59285</t>
+          <t>58383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,82 +2906,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>41040</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32093</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>50923</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>89200</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>76297</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>103101</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>18,86%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>41040</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>52187</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>25,84%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>89200</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>74893</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>102915</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>18,51%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20852</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>33148</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84357</t>
+          <t>84944</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28901</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>41948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72938</t>
+          <t>72856</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262610</t>
+          <t>263257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>303782</t>
+          <t>302972</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255898</t>
+          <t>257422</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>300149</t>
+          <t>298582</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>530073</t>
+          <t>531491</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>589514</t>
+          <t>592603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>127320</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>168168</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>122202</t>
+          <t>122620</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157814</t>
+          <t>157571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>262721</t>
+          <t>262000</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310707</t>
+          <t>311277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102509</t>
+          <t>103738</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135199</t>
+          <t>135123</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136504</t>
+          <t>137286</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>215554</t>
+          <t>215037</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>261279</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>30202</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51483</t>
+          <t>52114</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>51185</t>
+          <t>50427</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>75573</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87039</t>
+          <t>87210</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>120807</t>
+          <t>121655</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>86629</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>117310</t>
+          <t>119654</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>110408</t>
+          <t>109838</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>144943</t>
+          <t>144588</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>207211</t>
+          <t>206712</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252557</t>
+          <t>250885</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>63810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50489</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71790</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101043</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127709</t>
+          <t>128961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48027</t>
+          <t>48263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53180</t>
+          <t>52054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70753</t>
+          <t>70414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96508</t>
+          <t>95710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>16061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79972</t>
+          <t>79019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101640</t>
+          <t>100869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82737</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>106367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169985</t>
+          <t>168722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>202028</t>
+          <t>201063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49302</t>
+          <t>49729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70222</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101738</t>
+          <t>100806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129215</t>
+          <t>129712</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37219</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69038</t>
+          <t>69151</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>30112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>60358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>64790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83625</t>
+          <t>83946</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65451</t>
+          <t>65958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86944</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134969</t>
+          <t>134847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164241</t>
+          <t>164172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54926</t>
+          <t>56053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>43591</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64535</t>
+          <t>62376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86297</t>
+          <t>86583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113856</t>
+          <t>112256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44661</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15881</t>
+          <t>15648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>30077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80120</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104064</t>
+          <t>102638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81287</t>
+          <t>80525</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104979</t>
+          <t>104703</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167494</t>
+          <t>167101</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200739</t>
+          <t>201860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>44594</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66576</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>49715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71770</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101496</t>
+          <t>101762</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132604</t>
+          <t>134056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>33261</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54135</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23427</t>
+          <t>22202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36739</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30404</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38373</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>60539</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>289621</t>
+          <t>289816</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>333482</t>
+          <t>332066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>302122</t>
+          <t>303266</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>347948</t>
+          <t>344895</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>602629</t>
+          <t>601467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>665812</t>
+          <t>660577</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>176306</t>
+          <t>177377</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>215474</t>
+          <t>215385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195438</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>237246</t>
+          <t>236489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>386831</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>441894</t>
+          <t>442247</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>73072</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>103446</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>75582</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104913</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157603</t>
+          <t>157755</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>197712</t>
+          <t>197887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26110</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45057</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70024</t>
+          <t>69743</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>91152</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86002</t>
+          <t>86006</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>132218</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170907</t>
+          <t>172607</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
+          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21324</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30895</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8719</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>22501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>34027</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48029</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>66978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26347</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27849</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43345</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>50392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24019</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25821</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>29268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45179</t>
+          <t>45732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>18592</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>68931</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59502</t>
+          <t>59679</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>86420</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>145770</t>
+          <t>145954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>71439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>107507</t>
+          <t>105985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>138056</t>
+          <t>136862</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,44 +11098,44 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>6535</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>6541</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
